--- a/site/exports/nku-medical.xlsx
+++ b/site/exports/nku-medical.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,12 +443,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="19.6" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
@@ -569,10 +569,226 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>邢小龙</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>医学院/公共卫生与健康研究院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2024/0416/c6615a540332/page.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>现职、独立院系目录归属与本人求学导师未核；目前不提供现职导航。；仅保留本人页的研究者事实提取及最短引文，未保留完整原文；所选作品题名未知。；原单位合列医学院/公共卫生与健康研究院；这里只复用医学院展示节点，不由复合标签推行政父子关系。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>张敏英</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>医学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6614a69053/page.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>现职、独立院系目录归属与本人求学导师未核；目前不提供现职导航。；仅保留本人页的研究者事实提取及最短引文，未保留完整原文；所选作品题名未知。；职称栏教授与工作段副教授并存，未判定哪一项代表当前职级，也未推晋升日期。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>郭凤华</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>医学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69084/page.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>现职、独立院系目录归属与本人求学导师未核；目前不提供现职导航。；仅留存必要职业原文行，非完整页面；所选书目未核出版者元数据或全文。</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>王利凤</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>医学院</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69075/page.htm</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>现职、独立院系目录归属与本人求学导师未核；目前不提供现职导航。；仅留存必要职业原文行，非完整页面；所选书目未核出版者元数据或全文。</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,16 +800,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16.8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16.8" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -1038,14 +1254,940 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>邢小龙</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>医学学士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>中山大学公共卫生学院</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2010.9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2015.7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>本人教育记录列中山大学公共卫生学院、医学学士，按来源报告的具体资格记载；学习区间2010.9–2015.7。授位年月未知，不从学习末月推断，未核学位证。证据为已留存研究者事实提取，非完整原文；不据此补写原文授位动词或表头。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2024/0416/c6615a540332/page.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>邢小龙</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>医学博士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>北京协和医学院阜外医院/国家心血管病中心</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2015.8</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2021.6</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>本人教育记录列北京协和医学院阜外医院/国家心血管病中心、医学博士，按来源报告的具体资格记载；学习区间2015.8–2021.6。授位年月未知，不从学习末月推断，未核学位证。证据为已留存研究者事实提取，非完整原文；不据此补写原文授位动词或表头。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2024/0416/c6615a540332/page.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>邢小龙</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>南开大学医学院/公共卫生与健康研究院</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>原工作段：南开大学医学院/公共卫生与健康研究院，讲师，2021.7至今。“至今”为来源陈述，未独立核验目前在岗。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2024/0416/c6615a540332/page.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>张敏英</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>河北医科大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1990.9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1995.6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>原教育记录列河北医科大学、本科，学习区间1990.9–1995.6；授位年月未知，不从学习末月推断。依据已留存事实提取，不冒充完整原文。</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6614a69053/page.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>张敏英</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>中国预防医学科学院</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1999.9</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2002.6</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>流行病学与卫生统计学</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>本人教育记录列中国预防医学科学院、硕士，按来源报告的具体资格记载；学习区间1999.9–2002.6。授位年月未知，不从学习末月推断，未核学位证。证据为已留存研究者事实提取，非完整原文；不据此补写原文授位动词或表头。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6614a69053/page.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>张敏英</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>天津医科大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2003.9</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2006.6</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>流行病学专业</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>本人教育记录列天津医科大学、博士，按来源报告的具体资格记载；学习区间2003.9–2006.6。授位年月未知，不从学习末月推断，未核学位证。证据为已留存研究者事实提取，非完整原文；不据此补写原文授位动词或表头。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6614a69053/page.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>张敏英</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>南开大学医学院</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2007-07</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>原工作段：南开大学医学院，副教授，2007.7-。原终点空缺，未独立核验目前在岗。同页职称栏列教授、该工作段列副教授；两说保留，晋升日期与当前职级未知。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6614a69053/page.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>郭凤华</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>山西医科大学公共卫生学院</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1992.9</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1997.7</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>预防医学专业</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>原教育记录列山西医科大学公共卫生学院、本科，学习区间1992.9–1997.7；授位年月未知，不从学习末月推断。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69084/page.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>郭凤华</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>山西医科大学公共卫生学院</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1997.9</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2000.7</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>劳动卫生与环境卫生学专业</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>本人教育记录列山西医科大学公共卫生学院、硕士，按来源报告的具体资格记载；学习区间1997.9–2000.7。授位年月未知，不从学习末月推断，未核学位证。原文为教育经历逐项列举，不补授位动词。</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69084/page.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>郭凤华</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>中国疾病预防控制中心传染病预防控制所</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2004.9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2007.7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>病原生物学专业</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>本人教育记录列中国疾病预防控制中心传染病预防控制所、博士，按来源报告的具体资格记载；学习区间2004.9–2007.7。授位年月未知，不从学习末月推断，未核学位证。原文为教育经历逐项列举，不补授位动词。</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69084/page.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>郭凤华</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>南开大学医学院</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2007-07</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>原工作段：南开大学医学院，讲师，2007.7-。原终点空缺，未独立核验目前在岗。</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69084/page.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>郭凤华</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>助教、讲师</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>山西医科大学公共卫生学院</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2000.7</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2004.8</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>原2000.7–2004.8山西医科大学公共卫生学院助教、讲师为一个合并时段；未拆分两职级任期或推定晋升日期。</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69084/page.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>王利凤</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>山东大学生命科学学院</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2002.9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2007.7</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>发育生物学专业</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>本人教育记录列山东大学生命科学学院、博士，按来源报告的具体资格记载；学习区间2002.9–2007.7。授位年月未知，不从学习末月推断，未核学位证。原文为教育经历逐项列举，不补授位动词。</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69075/page.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>王利凤</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>南开大学医学院</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2007-07</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>原工作段：南开大学医学院，讲师，2007.7-至今。“至今”为来源陈述，未独立核验目前在岗。另原列2021.9–至今南开大学周恩来政府管理学院应用心理学专业硕士导师，为本人指导资格，不另计雇佣任职或本人求学导师，当前资格未独立核验。</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69075/page.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1148,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1331,13 +2473,275 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>邢小龙</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2024/0416/c6615a540332/page.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>原书目：BMC Public Health，2024年。原卷24。原文章号46。原列作者首位Xing X；题名在已留存提取中未得到支持，保持未知；完整作者表未核。仅个人页所列书目，出版者元数据与全文未核。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>张敏英</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6614a69053/page.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>原书目：BMC cardiovascular disorders，2021年。原卷21。原文章号291。原作者序列末项Minying Zhang*；星号含义未核，不推通讯作者。题名在已留存提取中未得到支持，保持未知；完整作者表未核。仅个人页所列书目，出版者元数据与全文未核。</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>郭凤华</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>hTERT rs2736098 genetic variants and susceptibility of hepatocellular carcinoma in the Chinese population: a case-control study</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69084/page.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>原书目：Hepatobiliary &amp; Pancreatic Diseases International，2013年。原卷12。原期1。原页74-79。原署名：Chao Zhang, Ya-Ping Tian, Yue Wang, Feng-Hua Guo, Jun-Fang Qin and Hong Ni。Feng-Hua Guo为所列合作者；未独立核完整作者表。仅个人页所列书目，出版者元数据与全文未核。</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>郭凤华</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>纳米碳化钨对斑马鱼胚胎发育的影响</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69084/page.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>原署名王利凤、郭凤华、杨卓；中国环境科学，2012年32卷7期，1280–1283页。仅本人页书目记录，未外核完整作者表或出版者元数据、未读全文，不按排序推通讯或共同第一作者。郭凤华与王利凤两人均列同一2012作品，此为各人物书目记录，不是两篇不同作品。</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>王利凤</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Toxicity of polymer-modified CuS nanoclusters on zebrafish embryo development</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69075/page.htm</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>原书目：J Appl Toxicol，2021年。原页1–10。原署名：Qiuping Zhang,Lifeng Wang*，Dongyan Chen etc.。原明确星号表示共同第一作者，保留本人共同第一作者角色，不推通讯作者；卷期未列，作者表含etc.并非完整名单。仅个人页所列书目，出版者元数据与全文未核。</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>王利凤</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>纳米碳化钨对斑马鱼胚胎发育的影响</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69075/page.htm</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>原署名王利凤、郭凤华、杨卓；中国环境科学，2012年32卷7期，1280–1283页。仅本人页书目记录，未外核完整作者表或出版者元数据、未读全文，不按排序推通讯或共同第一作者。郭凤华与王利凤两人均列同一2012作品，此为各人物书目记录，不是两篇不同作品。</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1349,7 +2753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1472,11 +2876,147 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>邢小龙</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>nankai-1-375</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2024/0416/c6615a540332/page.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>张敏英</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>nankai-2-375</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6614a69053/page.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>郭凤华</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>nankai-1-376</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69084/page.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>王利凤</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>nankai-2-376</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://medical.nankai.edu.cn/2017/0622/c6615a69075/page.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
